--- a/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0003T0006Z000C1N80_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0003T0006Z000C1N80_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>58.36167220063176</v>
+        <v>9.48377173260266</v>
       </c>
       <c r="D2" t="n">
-        <v>11.76860229593982</v>
+        <v>1.912397873090221</v>
       </c>
       <c r="E2" t="n">
-        <v>12.89648929100079</v>
+        <v>2.095679509787628</v>
       </c>
       <c r="F2" t="n">
-        <v>11.63020890052668</v>
+        <v>1.889908946335585</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>44.18884518211031</v>
+        <v>7.180687342092926</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>0.8125</v>
       </c>
       <c r="E3" t="n">
-        <v>12.89648929100079</v>
+        <v>2.095679509787628</v>
       </c>
       <c r="F3" t="n">
-        <v>11.63020890052668</v>
+        <v>1.889908946335585</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>39.35216918817898</v>
+        <v>6.394727493079084</v>
       </c>
       <c r="D4" t="n">
-        <v>7.648529270389178</v>
+        <v>1.242886006438241</v>
       </c>
       <c r="E4" t="n">
-        <v>12.89648929100079</v>
+        <v>2.095679509787628</v>
       </c>
       <c r="F4" t="n">
-        <v>11.63020890052668</v>
+        <v>1.889908946335585</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>39.229712326951</v>
+        <v>6.374828253129537</v>
       </c>
       <c r="D5" t="n">
-        <v>21.50581316760657</v>
+        <v>3.494694639736068</v>
       </c>
       <c r="E5" t="n">
-        <v>12.89648929100079</v>
+        <v>2.095679509787628</v>
       </c>
       <c r="F5" t="n">
-        <v>11.63020890052668</v>
+        <v>1.889908946335585</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>35.73841697508773</v>
+        <v>5.807492758451756</v>
       </c>
       <c r="D6" t="n">
-        <v>38.22050527756327</v>
+        <v>6.210832107604031</v>
       </c>
       <c r="E6" t="n">
-        <v>12.89648929100079</v>
+        <v>2.095679509787628</v>
       </c>
       <c r="F6" t="n">
-        <v>11.63020890052668</v>
+        <v>1.889908946335585</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>41.67979097123024</v>
+        <v>6.772966032824915</v>
       </c>
       <c r="D7" t="n">
-        <v>35.73845430102445</v>
+        <v>5.807498823916474</v>
       </c>
       <c r="E7" t="n">
-        <v>12.89648929100079</v>
+        <v>2.095679509787628</v>
       </c>
       <c r="F7" t="n">
-        <v>11.63020890052668</v>
+        <v>1.889908946335585</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>29.51306112774671</v>
+        <v>4.795872433258841</v>
       </c>
       <c r="D8" t="n">
-        <v>26.6800506451753</v>
+        <v>4.335508229840986</v>
       </c>
       <c r="E8" t="n">
-        <v>12.89648929100079</v>
+        <v>2.095679509787628</v>
       </c>
       <c r="F8" t="n">
-        <v>11.63020890052668</v>
+        <v>1.889908946335585</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>25.56281946110574</v>
+        <v>4.153958162429683</v>
       </c>
       <c r="D9" t="n">
-        <v>22.0976593263972</v>
+        <v>3.590869640539545</v>
       </c>
       <c r="E9" t="n">
-        <v>12.89648929100079</v>
+        <v>2.095679509787628</v>
       </c>
       <c r="F9" t="n">
-        <v>11.63020890052668</v>
+        <v>1.889908946335585</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>16.0701586799882</v>
+        <v>2.611400785498082</v>
       </c>
       <c r="D10" t="n">
-        <v>14.22071172534302</v>
+        <v>2.310865655368241</v>
       </c>
       <c r="E10" t="n">
-        <v>12.89648929100079</v>
+        <v>2.095679509787628</v>
       </c>
       <c r="F10" t="n">
-        <v>11.63020890052668</v>
+        <v>1.889908946335585</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>38.10155146437178</v>
+        <v>6.191502112960414</v>
       </c>
       <c r="D11" t="n">
-        <v>37.67563286147479</v>
+        <v>6.122290339989654</v>
       </c>
       <c r="E11" t="n">
-        <v>12.89648929100079</v>
+        <v>2.095679509787628</v>
       </c>
       <c r="F11" t="n">
-        <v>11.63020890052668</v>
+        <v>1.889908946335585</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>17.00735135169495</v>
+        <v>2.763694594650429</v>
       </c>
       <c r="D12" t="n">
-        <v>17.5520108939048</v>
+        <v>2.852201770259529</v>
       </c>
       <c r="E12" t="n">
-        <v>12.89648929100079</v>
+        <v>2.095679509787628</v>
       </c>
       <c r="F12" t="n">
-        <v>11.63020890052668</v>
+        <v>1.889908946335585</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>25.92300938051435</v>
+        <v>4.212489024333583</v>
       </c>
       <c r="D13" t="n">
-        <v>19.63471028033887</v>
+        <v>3.190640420555066</v>
       </c>
       <c r="E13" t="n">
-        <v>12.89648929100079</v>
+        <v>2.095679509787628</v>
       </c>
       <c r="F13" t="n">
-        <v>11.63020890052668</v>
+        <v>1.889908946335585</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>31.64253466459348</v>
+        <v>5.141911882996441</v>
       </c>
       <c r="D14" t="n">
-        <v>38.44976199576357</v>
+        <v>6.248086324311581</v>
       </c>
       <c r="E14" t="n">
-        <v>12.89648929100079</v>
+        <v>2.095679509787628</v>
       </c>
       <c r="F14" t="n">
-        <v>11.63020890052668</v>
+        <v>1.889908946335585</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>4.625229072761466</v>
+        <v>0.7515997243237383</v>
       </c>
       <c r="D15" t="n">
-        <v>5.401060122111142</v>
+        <v>0.8776722698430606</v>
       </c>
       <c r="E15" t="n">
-        <v>12.89648929100079</v>
+        <v>2.095679509787628</v>
       </c>
       <c r="F15" t="n">
-        <v>11.63020890052668</v>
+        <v>1.889908946335585</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>22.24394645486878</v>
+        <v>3.614641298916177</v>
       </c>
       <c r="D16" t="n">
-        <v>30.82739324794105</v>
+        <v>5.00945140279042</v>
       </c>
       <c r="E16" t="n">
-        <v>12.89648929100079</v>
+        <v>2.095679509787628</v>
       </c>
       <c r="F16" t="n">
-        <v>11.63020890052668</v>
+        <v>1.889908946335585</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
